--- a/data/annotations.xlsx
+++ b/data/annotations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1121,9 +1121,47 @@
         <v>Dr Essafi</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>IDRiD_075.jpg</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Proliferative DR</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/annotations.xlsx
+++ b/data/annotations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -781,16 +781,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>IDRiD_295.jpg</v>
+        <v>IDRiD_071.jpg</v>
       </c>
       <c r="B11" t="str">
-        <v>Moderate</v>
+        <v>Mild</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -811,33 +811,33 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="L11" t="str">
-        <v>Dr Boulanouar</v>
+        <v>Dr Essafi</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>IDRiD_071.jpg</v>
+        <v>IDRiD_072.jpg</v>
       </c>
       <c r="B12" t="str">
-        <v>Mild</v>
+        <v>Moderate</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="L12" t="str">
         <v>Dr Essafi</v>
@@ -857,25 +857,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>IDRiD_072.jpg</v>
+        <v>IDRiD_072test.jpg</v>
       </c>
       <c r="B13" t="str">
-        <v>Moderate</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
+        <v>Mauvaise qualité</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L13" t="str">
         <v>Dr Essafi</v>
@@ -895,25 +895,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>IDRiD_072test.jpg</v>
+        <v>IDRiD_073.jpg</v>
       </c>
       <c r="B14" t="str">
-        <v>Mauvaise qualité</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
+        <v>Moderate</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -925,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="str">
         <v>Dr Essafi</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>IDRiD_073.jpg</v>
+        <v>IDRiD_073test.jpg</v>
       </c>
       <c r="B15" t="str">
         <v>Moderate</v>
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="L15" t="str">
         <v>Dr Essafi</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>IDRiD_073test.jpg</v>
+        <v>IDRiD_014test.jpg</v>
       </c>
       <c r="B16" t="str">
         <v>Moderate</v>
@@ -980,16 +980,16 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1001,21 +1001,21 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="L16" t="str">
-        <v>Dr Essafi</v>
+        <v>Dr Hafidi</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>IDRiD_014test.jpg</v>
+        <v>IDRiD_074.jpg</v>
       </c>
       <c r="B17" t="str">
-        <v>Moderate</v>
+        <v>Proliferative DR</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1039,15 +1039,15 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="L17" t="str">
-        <v>Dr Hafidi</v>
+        <v>Dr Essafi</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>IDRiD_074.jpg</v>
+        <v>IDRiD_074test.jpg</v>
       </c>
       <c r="B18" t="str">
         <v>Proliferative DR</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>IDRiD_074test.jpg</v>
+        <v>IDRiD_075.jpg</v>
       </c>
       <c r="B19" t="str">
         <v>Proliferative DR</v>
@@ -1123,19 +1123,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>IDRiD_075.jpg</v>
+        <v>IDRiD_076.jpg</v>
       </c>
       <c r="B20" t="str">
-        <v>Proliferative DR</v>
+        <v>Moderate</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1156,12 +1156,316 @@
         <v>1</v>
       </c>
       <c r="L20" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>IDRiD_076test.jpg</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0.7</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>IDRiD_077.jpg</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Moderate</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>IDRiD_078.jpg</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.7</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>IDRiD_078test.jpg</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0.3</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>IDRiD_079.jpg</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0.7</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>IDRiD_079test.jpg</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0.3</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>IDRiD_080.jpg</v>
+      </c>
+      <c r="B27" t="str">
+        <v>No DR</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>IDRiD_080test.jpg</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0.7</v>
+      </c>
+      <c r="L28" t="str">
         <v>Dr Essafi</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/annotations.xlsx
+++ b/data/annotations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,22 +439,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>IDRiD_001test.jpg</v>
+        <v>IDRiD_014test.jpg</v>
       </c>
       <c r="B2" t="str">
-        <v>Severe</v>
+        <v>Moderate</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -469,27 +469,27 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L2" t="str">
-        <v>Dr Zekraoui</v>
+        <v>Dr Hafidi</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>IDRiD_014test.jpg</v>
+        <v>IDRiD_066test.jpg</v>
       </c>
       <c r="B3" t="str">
-        <v>Moderate</v>
+        <v>Severe</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -498,7 +498,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -510,12 +510,430 @@
         <v>0.3</v>
       </c>
       <c r="L3" t="str">
-        <v>Dr Hafidi</v>
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>IDRiD_067.jpg</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.7</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>IDRiD_067test.jpg</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0.3</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>IDRiD_068.jpg</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.3</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>IDRiD_068test.jpg</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Mild</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.7</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>IDRiD_069.jpg</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Mild</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>IDRiD_069test.jpg</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Moderate</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.7</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>IDRiD_070.jpg</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Proliferative DR</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.3</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>IDRiD_071.jpg</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Autre pathologie</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.3</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>IDRiD_072.jpg</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Mauvaise qualité</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0.3</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>IDRiD_072test.jpg</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Impacts laser</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0.7</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>IDRiD_073.jpg</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Severe</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0.3</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Dr Essafi</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>